--- a/excel/ReactTest.xlsx
+++ b/excel/ReactTest.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
   <si>
     <t>Match</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>WonWon</t>
+  </si>
+  <si>
+    <t>hahaha</t>
   </si>
 </sst>
 </file>
@@ -635,7 +638,8 @@
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="5" customFormat="1" ht="39.950000000000003" customHeight="1">
@@ -752,7 +756,9 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -1315,7 +1321,9 @@
       <c r="C11" s="19"/>
     </row>
     <row r="12" spans="1:8" ht="18">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
     </row>
